--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N101_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N101_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>91.3462019774357</v>
+        <v>14.8437578213333</v>
       </c>
       <c r="D2" t="n">
-        <v>55.70435948602579</v>
+        <v>9.051958416479192</v>
       </c>
       <c r="E2" t="n">
-        <v>20.62967061989433</v>
+        <v>3.352321475732829</v>
       </c>
       <c r="F2" t="n">
-        <v>17.58106727262859</v>
+        <v>2.856923431802145</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.76989176392564</v>
+        <v>8.737607411637917</v>
       </c>
       <c r="D3" t="n">
-        <v>13.51492568530595</v>
+        <v>2.196175423862217</v>
       </c>
       <c r="E3" t="n">
-        <v>20.62967061989433</v>
+        <v>3.352321475732829</v>
       </c>
       <c r="F3" t="n">
-        <v>17.58106727262859</v>
+        <v>2.856923431802145</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.24189352213518</v>
+        <v>6.376807697346967</v>
       </c>
       <c r="D4" t="n">
-        <v>34.71704560177177</v>
+        <v>5.641519910287913</v>
       </c>
       <c r="E4" t="n">
-        <v>20.62967061989433</v>
+        <v>3.352321475732829</v>
       </c>
       <c r="F4" t="n">
-        <v>17.58106727262859</v>
+        <v>2.856923431802145</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.05880896418495</v>
+        <v>8.134556456680055</v>
       </c>
       <c r="D5" t="n">
-        <v>15.18131161073451</v>
+        <v>2.466963136744357</v>
       </c>
       <c r="E5" t="n">
-        <v>20.62967061989433</v>
+        <v>3.352321475732829</v>
       </c>
       <c r="F5" t="n">
-        <v>17.58106727262859</v>
+        <v>2.856923431802145</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.86952302773108</v>
+        <v>7.453797492006301</v>
       </c>
       <c r="D6" t="n">
-        <v>35.31603350069516</v>
+        <v>5.738855443862963</v>
       </c>
       <c r="E6" t="n">
-        <v>20.62967061989433</v>
+        <v>3.352321475732829</v>
       </c>
       <c r="F6" t="n">
-        <v>17.58106727262859</v>
+        <v>2.856923431802145</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.55316384973993</v>
+        <v>3.827389125582739</v>
       </c>
       <c r="D7" t="n">
-        <v>58.94208817035044</v>
+        <v>9.578089327681948</v>
       </c>
       <c r="E7" t="n">
-        <v>20.62967061989433</v>
+        <v>3.352321475732829</v>
       </c>
       <c r="F7" t="n">
-        <v>17.58106727262859</v>
+        <v>2.856923431802145</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
